--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N91_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N91_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.13541867050605</v>
+        <v>4.247005533957234</v>
       </c>
       <c r="D2" t="n">
-        <v>26.5118122304319</v>
+        <v>4.308169487445184</v>
       </c>
       <c r="E2" t="n">
-        <v>22.26529385796844</v>
+        <v>3.618110251919873</v>
       </c>
       <c r="F2" t="n">
-        <v>16.01330382074316</v>
+        <v>2.602161870870764</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>68.75312088753837</v>
+        <v>11.17238214422499</v>
       </c>
       <c r="D3" t="n">
-        <v>51.90020294526447</v>
+        <v>8.433782978605477</v>
       </c>
       <c r="E3" t="n">
-        <v>22.26529385796844</v>
+        <v>3.618110251919873</v>
       </c>
       <c r="F3" t="n">
-        <v>16.01330382074316</v>
+        <v>2.602161870870764</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7.371516224622533</v>
+        <v>1.197871386501162</v>
       </c>
       <c r="D4" t="n">
-        <v>7.691386660850799</v>
+        <v>1.249850332388255</v>
       </c>
       <c r="E4" t="n">
-        <v>22.26529385796844</v>
+        <v>3.618110251919873</v>
       </c>
       <c r="F4" t="n">
-        <v>16.01330382074316</v>
+        <v>2.602161870870764</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.47794329589735</v>
+        <v>5.92766578558332</v>
       </c>
       <c r="D5" t="n">
-        <v>36.12220161613963</v>
+        <v>5.869857762622691</v>
       </c>
       <c r="E5" t="n">
-        <v>22.26529385796844</v>
+        <v>3.618110251919873</v>
       </c>
       <c r="F5" t="n">
-        <v>16.01330382074316</v>
+        <v>2.602161870870764</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
